--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NG4537\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicoerosanna/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA08F15-BE62-47A2-A066-9F115E253A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761AF600-AE6C-7A41-8637-6676E943E24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Originale" sheetId="1" r:id="rId1"/>
@@ -5635,9 +5635,6 @@
     <t>LBMA</t>
   </si>
   <si>
-    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/gold/LBMA-gold_M-gold_M_EUR_AM_AVG.csv</t>
-  </si>
-  <si>
     <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/899903%20-%20MSCI%20AC%20Asia%20Pacific%20ex%20Japan%20Index%20.xlsx</t>
   </si>
   <si>
@@ -5772,6 +5769,9 @@
   </si>
   <si>
     <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/664204%20-%20MSCI%20ACWI%20IMI%20Index.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/gold/Gold_price_averages_in_a%20range_of_currencies_since_1978.xlsx</t>
   </si>
 </sst>
 </file>
@@ -5875,61 +5875,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -5974,6 +5920,44 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5994,7 +5978,7 @@
     <sortCondition ref="A1:A800"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D73B884A-503A-4A59-8C87-18B439C847EE}" name="id" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{D73B884A-503A-4A59-8C87-18B439C847EE}" name="id" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{5A90A855-91ED-41CE-B4B6-41473BC05892}" name="name"/>
     <tableColumn id="3" xr3:uid="{A6DB99C2-C65F-4DE9-8199-32DE52DA7D1D}" name="url"/>
   </tableColumns>
@@ -6014,31 +5998,31 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}" name="Table1" displayName="Table1" ref="B2:C30" totalsRowShown="0" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}" name="Table1" displayName="Table1" ref="B2:C30" totalsRowShown="0" dataDxfId="2">
   <autoFilter ref="B2:C30" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2DEF44DB-B91A-4361-87EC-E5D8D821409D}" name="Aree" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{8FBA11E1-52C6-43A5-A4B9-0B712AC388F0}" name="Note" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{2DEF44DB-B91A-4361-87EC-E5D8D821409D}" name="Aree" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{8FBA11E1-52C6-43A5-A4B9-0B712AC388F0}" name="Note" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}" name="Table2" displayName="Table2" ref="A1:H80" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}" name="Table2" displayName="Table2" ref="A1:H80" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:H80" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H79">
-    <sortCondition sortBy="cellColor" ref="G1:G79" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="G1:G79" dxfId="12"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{60FD31BC-5634-4AC8-90B2-A3D616FBC3D6}" name="Country/Area" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{540470DD-A2B3-4E39-8556-EA289CFDD467}" name="ETF" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{D752676A-DDD5-4EF0-B155-46198ABE56FB}" name="Note" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{67AF040E-FE41-4ECF-B4E6-99DBE8F70E46}" name="Data label" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{B3443B95-6046-496C-8F37-29C6A0B5F077}" name="Data source" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{3D3BC678-D548-42C9-BDDE-6FBC4D8160B8}" name="Yahoo" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{66183E1C-249B-4B92-B75F-97E586BFDF95}" name="Link" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{89FD6C47-21B3-47AF-97FD-B2BF9E03DF02}" name="Original source" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{60FD31BC-5634-4AC8-90B2-A3D616FBC3D6}" name="Country/Area" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{540470DD-A2B3-4E39-8556-EA289CFDD467}" name="ETF" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{D752676A-DDD5-4EF0-B155-46198ABE56FB}" name="Note" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{67AF040E-FE41-4ECF-B4E6-99DBE8F70E46}" name="Data label" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{B3443B95-6046-496C-8F37-29C6A0B5F077}" name="Data source" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{3D3BC678-D548-42C9-BDDE-6FBC4D8160B8}" name="Yahoo" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{66183E1C-249B-4B92-B75F-97E586BFDF95}" name="Link" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{89FD6C47-21B3-47AF-97FD-B2BF9E03DF02}" name="Original source" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6330,14 +6314,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C800"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="86.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.42578125" customWidth="1"/>
+    <col min="2" max="2" width="86.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1777</v>
       </c>
@@ -6348,7 +6332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -6359,7 +6343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -6370,7 +6354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6381,7 +6365,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -6392,7 +6376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -6403,7 +6387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -6414,7 +6398,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -6425,7 +6409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -6436,7 +6420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -6447,7 +6431,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -6458,7 +6442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -6469,7 +6453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -6480,7 +6464,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -6491,7 +6475,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -6502,7 +6486,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -6513,7 +6497,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -6524,7 +6508,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -6535,7 +6519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -6546,7 +6530,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -6557,7 +6541,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -6568,7 +6552,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -6579,7 +6563,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -6590,7 +6574,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -6601,7 +6585,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -6612,7 +6596,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -6623,7 +6607,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -6634,7 +6618,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -6645,7 +6629,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -6656,7 +6640,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -6667,7 +6651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -6678,7 +6662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -6689,7 +6673,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -6700,7 +6684,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -6711,7 +6695,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -6722,7 +6706,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -6733,7 +6717,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -6744,7 +6728,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -6755,7 +6739,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -6766,7 +6750,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -6777,7 +6761,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -6788,7 +6772,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -6799,7 +6783,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -6810,7 +6794,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -6821,7 +6805,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -6832,7 +6816,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -6843,7 +6827,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -6854,7 +6838,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -6865,7 +6849,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6876,7 +6860,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6887,7 +6871,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6898,7 +6882,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6909,7 +6893,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6920,7 +6904,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6931,7 +6915,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -6942,7 +6926,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -6953,7 +6937,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -6964,7 +6948,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -6975,7 +6959,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6986,7 +6970,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6997,7 +6981,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -7008,7 +6992,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -7019,7 +7003,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -7030,7 +7014,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -7041,7 +7025,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -7052,7 +7036,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -7063,7 +7047,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -7074,7 +7058,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -7085,7 +7069,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -7096,7 +7080,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -7107,7 +7091,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -7118,7 +7102,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -7129,7 +7113,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -7140,7 +7124,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -7151,7 +7135,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -7162,7 +7146,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -7173,7 +7157,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -7184,7 +7168,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -7195,7 +7179,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -7206,7 +7190,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -7217,7 +7201,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -7228,7 +7212,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -7239,7 +7223,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -7250,7 +7234,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -7261,7 +7245,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -7272,7 +7256,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -7283,7 +7267,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -7294,7 +7278,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -7305,7 +7289,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -7316,7 +7300,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -7327,7 +7311,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -7338,7 +7322,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -7349,7 +7333,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -7360,7 +7344,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -7371,7 +7355,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -7382,7 +7366,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -7393,7 +7377,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -7404,7 +7388,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -7415,7 +7399,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -7426,7 +7410,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -7437,7 +7421,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -7448,7 +7432,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -7459,7 +7443,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -7470,7 +7454,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -7481,7 +7465,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -7492,7 +7476,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -7503,7 +7487,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -7514,7 +7498,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -7525,7 +7509,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -7536,7 +7520,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -7547,7 +7531,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -7558,7 +7542,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -7569,7 +7553,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -7580,7 +7564,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -7591,7 +7575,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -7602,7 +7586,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -7613,7 +7597,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -7624,7 +7608,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -7635,7 +7619,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -7646,7 +7630,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -7657,7 +7641,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -7668,7 +7652,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -7679,7 +7663,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -7690,7 +7674,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -7701,7 +7685,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -7712,7 +7696,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -7723,7 +7707,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -7734,7 +7718,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -7745,7 +7729,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -7756,7 +7740,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -7767,7 +7751,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -7778,7 +7762,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -7789,7 +7773,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -7800,7 +7784,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -7811,7 +7795,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -7822,7 +7806,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -7833,7 +7817,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -7844,7 +7828,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -7855,7 +7839,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -7866,7 +7850,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -7877,7 +7861,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -7888,7 +7872,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -7899,7 +7883,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -7910,7 +7894,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -7921,7 +7905,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -7932,7 +7916,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -7943,7 +7927,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -7954,7 +7938,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -7965,7 +7949,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -7976,7 +7960,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -7987,7 +7971,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -7998,7 +7982,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -8009,7 +7993,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -8020,7 +8004,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -8031,7 +8015,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -8042,7 +8026,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -8053,7 +8037,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -8064,7 +8048,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -8075,7 +8059,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -8086,7 +8070,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -8097,7 +8081,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -8108,7 +8092,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -8119,7 +8103,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -8130,7 +8114,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -8141,7 +8125,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -8152,7 +8136,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -8163,7 +8147,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -8174,7 +8158,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -8185,7 +8169,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -8196,7 +8180,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -8207,7 +8191,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -8218,7 +8202,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -8229,7 +8213,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -8240,7 +8224,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -8251,7 +8235,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -8262,7 +8246,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -8273,7 +8257,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -8284,7 +8268,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -8295,7 +8279,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -8306,7 +8290,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -8317,7 +8301,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -8328,7 +8312,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -8339,7 +8323,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -8350,7 +8334,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -8361,7 +8345,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -8372,7 +8356,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -8383,7 +8367,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -8394,7 +8378,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -8405,7 +8389,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -8416,7 +8400,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -8427,7 +8411,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -8438,7 +8422,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -8449,7 +8433,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -8460,7 +8444,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -8471,7 +8455,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -8482,7 +8466,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -8493,7 +8477,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -8504,7 +8488,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -8515,7 +8499,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -8526,7 +8510,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -8537,7 +8521,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -8548,7 +8532,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -8559,7 +8543,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -8570,7 +8554,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -8581,7 +8565,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -8592,7 +8576,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -8603,7 +8587,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -8614,7 +8598,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -8625,7 +8609,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -8636,7 +8620,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -8647,7 +8631,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -8658,7 +8642,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -8669,7 +8653,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -8680,7 +8664,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -8691,7 +8675,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -8702,7 +8686,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -8713,7 +8697,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -8724,7 +8708,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -8735,7 +8719,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -8746,7 +8730,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -8757,7 +8741,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -8768,7 +8752,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -8779,7 +8763,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -8790,7 +8774,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -8801,7 +8785,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -8812,7 +8796,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -8823,7 +8807,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -8834,7 +8818,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -8845,7 +8829,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -8856,7 +8840,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -8867,7 +8851,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -8878,7 +8862,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>230</v>
       </c>
@@ -8889,7 +8873,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>231</v>
       </c>
@@ -8900,7 +8884,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>232</v>
       </c>
@@ -8911,7 +8895,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>233</v>
       </c>
@@ -8922,7 +8906,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>234</v>
       </c>
@@ -8933,7 +8917,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>235</v>
       </c>
@@ -8944,7 +8928,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>236</v>
       </c>
@@ -8955,7 +8939,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>237</v>
       </c>
@@ -8966,7 +8950,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>238</v>
       </c>
@@ -8977,7 +8961,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>239</v>
       </c>
@@ -8988,7 +8972,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>240</v>
       </c>
@@ -8999,7 +8983,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>241</v>
       </c>
@@ -9010,7 +8994,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>242</v>
       </c>
@@ -9021,7 +9005,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>243</v>
       </c>
@@ -9032,7 +9016,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>244</v>
       </c>
@@ -9043,7 +9027,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>245</v>
       </c>
@@ -9054,7 +9038,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>246</v>
       </c>
@@ -9065,7 +9049,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>247</v>
       </c>
@@ -9076,7 +9060,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>248</v>
       </c>
@@ -9087,7 +9071,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>249</v>
       </c>
@@ -9098,7 +9082,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>250</v>
       </c>
@@ -9109,7 +9093,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>251</v>
       </c>
@@ -9120,7 +9104,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>252</v>
       </c>
@@ -9131,7 +9115,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>253</v>
       </c>
@@ -9142,7 +9126,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>254</v>
       </c>
@@ -9153,7 +9137,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>255</v>
       </c>
@@ -9164,7 +9148,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>256</v>
       </c>
@@ -9175,7 +9159,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>257</v>
       </c>
@@ -9186,7 +9170,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>258</v>
       </c>
@@ -9197,7 +9181,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>259</v>
       </c>
@@ -9208,7 +9192,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>260</v>
       </c>
@@ -9219,7 +9203,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>261</v>
       </c>
@@ -9230,7 +9214,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>262</v>
       </c>
@@ -9241,7 +9225,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>263</v>
       </c>
@@ -9252,7 +9236,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>264</v>
       </c>
@@ -9263,7 +9247,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>265</v>
       </c>
@@ -9274,7 +9258,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>266</v>
       </c>
@@ -9285,7 +9269,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>267</v>
       </c>
@@ -9296,7 +9280,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>268</v>
       </c>
@@ -9307,7 +9291,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>269</v>
       </c>
@@ -9318,7 +9302,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>270</v>
       </c>
@@ -9329,7 +9313,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>271</v>
       </c>
@@ -9340,7 +9324,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>272</v>
       </c>
@@ -9351,7 +9335,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>273</v>
       </c>
@@ -9362,7 +9346,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>274</v>
       </c>
@@ -9373,7 +9357,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>275</v>
       </c>
@@ -9384,7 +9368,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>276</v>
       </c>
@@ -9395,7 +9379,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>277</v>
       </c>
@@ -9406,7 +9390,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>278</v>
       </c>
@@ -9417,7 +9401,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>279</v>
       </c>
@@ -9428,7 +9412,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>280</v>
       </c>
@@ -9439,7 +9423,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>281</v>
       </c>
@@ -9450,7 +9434,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>282</v>
       </c>
@@ -9461,7 +9445,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>283</v>
       </c>
@@ -9472,7 +9456,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>284</v>
       </c>
@@ -9483,7 +9467,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>285</v>
       </c>
@@ -9494,7 +9478,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>286</v>
       </c>
@@ -9505,7 +9489,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>287</v>
       </c>
@@ -9516,7 +9500,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>288</v>
       </c>
@@ -9527,7 +9511,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>289</v>
       </c>
@@ -9538,7 +9522,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>290</v>
       </c>
@@ -9549,7 +9533,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>291</v>
       </c>
@@ -9560,7 +9544,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>292</v>
       </c>
@@ -9571,7 +9555,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>293</v>
       </c>
@@ -9582,7 +9566,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>294</v>
       </c>
@@ -9593,7 +9577,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>295</v>
       </c>
@@ -9604,7 +9588,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>296</v>
       </c>
@@ -9615,7 +9599,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>297</v>
       </c>
@@ -9626,7 +9610,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>298</v>
       </c>
@@ -9637,7 +9621,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>299</v>
       </c>
@@ -9648,7 +9632,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>300</v>
       </c>
@@ -9659,7 +9643,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>301</v>
       </c>
@@ -9670,7 +9654,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>302</v>
       </c>
@@ -9681,7 +9665,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>303</v>
       </c>
@@ -9692,7 +9676,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>304</v>
       </c>
@@ -9703,7 +9687,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>305</v>
       </c>
@@ -9714,7 +9698,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>306</v>
       </c>
@@ -9725,7 +9709,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>307</v>
       </c>
@@ -9736,7 +9720,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>308</v>
       </c>
@@ -9747,7 +9731,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>309</v>
       </c>
@@ -9758,7 +9742,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>310</v>
       </c>
@@ -9769,7 +9753,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>311</v>
       </c>
@@ -9780,7 +9764,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>312</v>
       </c>
@@ -9791,7 +9775,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>313</v>
       </c>
@@ -9802,7 +9786,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>314</v>
       </c>
@@ -9813,7 +9797,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>315</v>
       </c>
@@ -9824,7 +9808,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>316</v>
       </c>
@@ -9835,7 +9819,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>317</v>
       </c>
@@ -9846,7 +9830,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>318</v>
       </c>
@@ -9857,7 +9841,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>319</v>
       </c>
@@ -9868,7 +9852,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>320</v>
       </c>
@@ -9879,7 +9863,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>321</v>
       </c>
@@ -9890,7 +9874,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>322</v>
       </c>
@@ -9901,7 +9885,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>323</v>
       </c>
@@ -9912,7 +9896,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>324</v>
       </c>
@@ -9923,7 +9907,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>325</v>
       </c>
@@ -9934,7 +9918,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>326</v>
       </c>
@@ -9945,7 +9929,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>327</v>
       </c>
@@ -9956,7 +9940,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>328</v>
       </c>
@@ -9967,7 +9951,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>329</v>
       </c>
@@ -9978,7 +9962,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>330</v>
       </c>
@@ -9989,7 +9973,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>331</v>
       </c>
@@ -10000,7 +9984,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>332</v>
       </c>
@@ -10011,7 +9995,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>333</v>
       </c>
@@ -10022,7 +10006,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>334</v>
       </c>
@@ -10033,7 +10017,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>335</v>
       </c>
@@ -10044,7 +10028,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>336</v>
       </c>
@@ -10055,7 +10039,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>337</v>
       </c>
@@ -10066,7 +10050,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>338</v>
       </c>
@@ -10077,7 +10061,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>339</v>
       </c>
@@ -10088,7 +10072,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>340</v>
       </c>
@@ -10099,7 +10083,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>341</v>
       </c>
@@ -10110,7 +10094,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>342</v>
       </c>
@@ -10121,7 +10105,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>343</v>
       </c>
@@ -10132,7 +10116,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>344</v>
       </c>
@@ -10143,7 +10127,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>345</v>
       </c>
@@ -10154,7 +10138,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>346</v>
       </c>
@@ -10165,7 +10149,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>347</v>
       </c>
@@ -10176,7 +10160,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>348</v>
       </c>
@@ -10187,7 +10171,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>349</v>
       </c>
@@ -10198,7 +10182,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>350</v>
       </c>
@@ -10209,7 +10193,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>351</v>
       </c>
@@ -10220,7 +10204,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>352</v>
       </c>
@@ -10231,7 +10215,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>353</v>
       </c>
@@ -10242,7 +10226,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>354</v>
       </c>
@@ -10253,7 +10237,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>355</v>
       </c>
@@ -10264,7 +10248,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>356</v>
       </c>
@@ -10275,7 +10259,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>357</v>
       </c>
@@ -10286,7 +10270,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>358</v>
       </c>
@@ -10297,7 +10281,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>359</v>
       </c>
@@ -10308,7 +10292,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>360</v>
       </c>
@@ -10319,7 +10303,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>361</v>
       </c>
@@ -10330,7 +10314,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>362</v>
       </c>
@@ -10341,7 +10325,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>363</v>
       </c>
@@ -10352,7 +10336,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>364</v>
       </c>
@@ -10363,7 +10347,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>365</v>
       </c>
@@ -10374,7 +10358,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>366</v>
       </c>
@@ -10385,7 +10369,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>367</v>
       </c>
@@ -10396,7 +10380,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>368</v>
       </c>
@@ -10407,7 +10391,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>369</v>
       </c>
@@ -10418,7 +10402,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>370</v>
       </c>
@@ -10429,7 +10413,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>371</v>
       </c>
@@ -10440,7 +10424,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>372</v>
       </c>
@@ -10451,7 +10435,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>373</v>
       </c>
@@ -10462,7 +10446,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>374</v>
       </c>
@@ -10473,7 +10457,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>375</v>
       </c>
@@ -10484,7 +10468,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>376</v>
       </c>
@@ -10495,7 +10479,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>377</v>
       </c>
@@ -10506,7 +10490,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>378</v>
       </c>
@@ -10517,7 +10501,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>379</v>
       </c>
@@ -10528,7 +10512,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>380</v>
       </c>
@@ -10539,7 +10523,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>381</v>
       </c>
@@ -10550,7 +10534,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>382</v>
       </c>
@@ -10561,7 +10545,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>383</v>
       </c>
@@ -10572,7 +10556,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>384</v>
       </c>
@@ -10583,7 +10567,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>385</v>
       </c>
@@ -10594,7 +10578,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>386</v>
       </c>
@@ -10605,7 +10589,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>387</v>
       </c>
@@ -10616,7 +10600,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>388</v>
       </c>
@@ -10627,7 +10611,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>389</v>
       </c>
@@ -10638,7 +10622,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>390</v>
       </c>
@@ -10649,7 +10633,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>391</v>
       </c>
@@ -10660,7 +10644,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>392</v>
       </c>
@@ -10671,7 +10655,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>393</v>
       </c>
@@ -10682,7 +10666,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>394</v>
       </c>
@@ -10693,7 +10677,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>395</v>
       </c>
@@ -10704,7 +10688,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>396</v>
       </c>
@@ -10715,7 +10699,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -10726,7 +10710,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -10737,7 +10721,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -10748,7 +10732,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -10759,7 +10743,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -10770,7 +10754,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>402</v>
       </c>
@@ -10781,7 +10765,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>403</v>
       </c>
@@ -10792,7 +10776,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>404</v>
       </c>
@@ -10803,7 +10787,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>405</v>
       </c>
@@ -10814,7 +10798,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>406</v>
       </c>
@@ -10825,7 +10809,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>407</v>
       </c>
@@ -10836,7 +10820,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>408</v>
       </c>
@@ -10847,7 +10831,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>409</v>
       </c>
@@ -10858,7 +10842,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>410</v>
       </c>
@@ -10869,7 +10853,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>411</v>
       </c>
@@ -10880,7 +10864,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>412</v>
       </c>
@@ -10891,7 +10875,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>413</v>
       </c>
@@ -10902,7 +10886,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
         <v>414</v>
       </c>
@@ -10913,7 +10897,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
         <v>415</v>
       </c>
@@ -10924,7 +10908,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>416</v>
       </c>
@@ -10935,7 +10919,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>417</v>
       </c>
@@ -10946,7 +10930,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>418</v>
       </c>
@@ -10957,7 +10941,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>419</v>
       </c>
@@ -10968,7 +10952,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>420</v>
       </c>
@@ -10979,7 +10963,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>421</v>
       </c>
@@ -10990,7 +10974,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>422</v>
       </c>
@@ -11001,7 +10985,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>423</v>
       </c>
@@ -11012,7 +10996,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>424</v>
       </c>
@@ -11023,7 +11007,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>425</v>
       </c>
@@ -11034,7 +11018,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
         <v>426</v>
       </c>
@@ -11045,7 +11029,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
         <v>427</v>
       </c>
@@ -11056,7 +11040,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
         <v>428</v>
       </c>
@@ -11067,7 +11051,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
         <v>429</v>
       </c>
@@ -11078,7 +11062,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
         <v>430</v>
       </c>
@@ -11089,7 +11073,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
         <v>431</v>
       </c>
@@ -11100,7 +11084,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
         <v>432</v>
       </c>
@@ -11111,7 +11095,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
         <v>433</v>
       </c>
@@ -11122,7 +11106,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
         <v>434</v>
       </c>
@@ -11133,7 +11117,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
         <v>435</v>
       </c>
@@ -11144,7 +11128,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
         <v>436</v>
       </c>
@@ -11155,7 +11139,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
         <v>437</v>
       </c>
@@ -11166,7 +11150,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
         <v>438</v>
       </c>
@@ -11177,7 +11161,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
         <v>439</v>
       </c>
@@ -11188,7 +11172,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
         <v>440</v>
       </c>
@@ -11199,7 +11183,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
         <v>441</v>
       </c>
@@ -11210,7 +11194,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
         <v>442</v>
       </c>
@@ -11221,7 +11205,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
         <v>443</v>
       </c>
@@ -11232,7 +11216,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
         <v>444</v>
       </c>
@@ -11243,7 +11227,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
         <v>445</v>
       </c>
@@ -11254,7 +11238,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
         <v>446</v>
       </c>
@@ -11265,7 +11249,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
         <v>447</v>
       </c>
@@ -11276,7 +11260,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
         <v>448</v>
       </c>
@@ -11287,7 +11271,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
         <v>449</v>
       </c>
@@ -11298,7 +11282,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
         <v>450</v>
       </c>
@@ -11309,7 +11293,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
         <v>451</v>
       </c>
@@ -11320,7 +11304,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
         <v>452</v>
       </c>
@@ -11331,7 +11315,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
         <v>453</v>
       </c>
@@ -11342,7 +11326,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
         <v>454</v>
       </c>
@@ -11353,7 +11337,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
         <v>455</v>
       </c>
@@ -11364,7 +11348,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
         <v>456</v>
       </c>
@@ -11375,7 +11359,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
         <v>457</v>
       </c>
@@ -11386,7 +11370,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
         <v>458</v>
       </c>
@@ -11397,7 +11381,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
         <v>459</v>
       </c>
@@ -11408,7 +11392,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
         <v>460</v>
       </c>
@@ -11419,7 +11403,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
         <v>461</v>
       </c>
@@ -11430,7 +11414,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="1">
         <v>462</v>
       </c>
@@ -11441,7 +11425,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A465" s="1">
         <v>463</v>
       </c>
@@ -11452,7 +11436,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A466" s="1">
         <v>464</v>
       </c>
@@ -11463,7 +11447,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A467" s="1">
         <v>465</v>
       </c>
@@ -11474,7 +11458,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A468" s="1">
         <v>466</v>
       </c>
@@ -11485,7 +11469,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A469" s="1">
         <v>467</v>
       </c>
@@ -11496,7 +11480,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A470" s="1">
         <v>468</v>
       </c>
@@ -11507,7 +11491,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A471" s="1">
         <v>469</v>
       </c>
@@ -11518,7 +11502,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A472" s="1">
         <v>470</v>
       </c>
@@ -11529,7 +11513,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A473" s="1">
         <v>471</v>
       </c>
@@ -11540,7 +11524,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A474" s="1">
         <v>472</v>
       </c>
@@ -11551,7 +11535,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="1">
         <v>473</v>
       </c>
@@ -11562,7 +11546,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A476" s="1">
         <v>474</v>
       </c>
@@ -11573,7 +11557,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A477" s="1">
         <v>475</v>
       </c>
@@ -11584,7 +11568,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A478" s="1">
         <v>476</v>
       </c>
@@ -11595,7 +11579,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
         <v>477</v>
       </c>
@@ -11606,7 +11590,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
         <v>478</v>
       </c>
@@ -11617,7 +11601,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
         <v>479</v>
       </c>
@@ -11628,7 +11612,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
         <v>480</v>
       </c>
@@ -11639,7 +11623,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
         <v>481</v>
       </c>
@@ -11650,7 +11634,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
         <v>482</v>
       </c>
@@ -11661,7 +11645,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A485" s="1">
         <v>483</v>
       </c>
@@ -11672,7 +11656,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="1">
         <v>484</v>
       </c>
@@ -11683,7 +11667,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A487" s="1">
         <v>485</v>
       </c>
@@ -11694,7 +11678,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A488" s="1">
         <v>486</v>
       </c>
@@ -11705,7 +11689,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A489" s="1">
         <v>487</v>
       </c>
@@ -11716,7 +11700,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A490" s="1">
         <v>488</v>
       </c>
@@ -11727,7 +11711,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A491" s="1">
         <v>489</v>
       </c>
@@ -11738,7 +11722,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A492" s="1">
         <v>490</v>
       </c>
@@ -11749,7 +11733,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A493" s="1">
         <v>491</v>
       </c>
@@ -11760,7 +11744,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A494" s="1">
         <v>492</v>
       </c>
@@ -11771,7 +11755,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A495" s="1">
         <v>493</v>
       </c>
@@ -11782,7 +11766,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A496" s="1">
         <v>494</v>
       </c>
@@ -11793,7 +11777,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="1">
         <v>495</v>
       </c>
@@ -11804,7 +11788,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A498" s="1">
         <v>496</v>
       </c>
@@ -11815,7 +11799,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A499" s="1">
         <v>497</v>
       </c>
@@ -11826,7 +11810,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A500" s="1">
         <v>498</v>
       </c>
@@ -11837,7 +11821,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A501" s="1">
         <v>499</v>
       </c>
@@ -11848,7 +11832,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A502" s="1">
         <v>500</v>
       </c>
@@ -11859,7 +11843,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
         <v>501</v>
       </c>
@@ -11870,7 +11854,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
         <v>502</v>
       </c>
@@ -11881,7 +11865,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
         <v>503</v>
       </c>
@@ -11892,7 +11876,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
         <v>504</v>
       </c>
@@ -11903,7 +11887,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
         <v>505</v>
       </c>
@@ -11914,7 +11898,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
         <v>506</v>
       </c>
@@ -11925,7 +11909,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
         <v>507</v>
       </c>
@@ -11936,7 +11920,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
         <v>508</v>
       </c>
@@ -11947,7 +11931,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
         <v>509</v>
       </c>
@@ -11958,7 +11942,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A512" s="1">
         <v>510</v>
       </c>
@@ -11969,7 +11953,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A513" s="1">
         <v>511</v>
       </c>
@@ -11980,7 +11964,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A514" s="1">
         <v>512</v>
       </c>
@@ -11991,7 +11975,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A515" s="1">
         <v>513</v>
       </c>
@@ -12002,7 +11986,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A516" s="1">
         <v>514</v>
       </c>
@@ -12013,7 +11997,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A517" s="1">
         <v>515</v>
       </c>
@@ -12024,7 +12008,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A518" s="1">
         <v>516</v>
       </c>
@@ -12035,7 +12019,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="1">
         <v>517</v>
       </c>
@@ -12046,7 +12030,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A520" s="1">
         <v>518</v>
       </c>
@@ -12057,7 +12041,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A521" s="1">
         <v>519</v>
       </c>
@@ -12068,7 +12052,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A522" s="1">
         <v>520</v>
       </c>
@@ -12079,7 +12063,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A523" s="1">
         <v>521</v>
       </c>
@@ -12090,7 +12074,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A524" s="1">
         <v>522</v>
       </c>
@@ -12101,7 +12085,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A525" s="1">
         <v>523</v>
       </c>
@@ -12112,7 +12096,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A526" s="1">
         <v>524</v>
       </c>
@@ -12123,7 +12107,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A527" s="1">
         <v>525</v>
       </c>
@@ -12134,7 +12118,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A528" s="1">
         <v>526</v>
       </c>
@@ -12145,7 +12129,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A529" s="1">
         <v>527</v>
       </c>
@@ -12156,7 +12140,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="1">
         <v>528</v>
       </c>
@@ -12167,7 +12151,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A531" s="1">
         <v>529</v>
       </c>
@@ -12178,7 +12162,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A532" s="1">
         <v>530</v>
       </c>
@@ -12189,7 +12173,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A533" s="1">
         <v>531</v>
       </c>
@@ -12200,7 +12184,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A534" s="1">
         <v>532</v>
       </c>
@@ -12211,7 +12195,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A535" s="1">
         <v>533</v>
       </c>
@@ -12222,7 +12206,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A536" s="1">
         <v>534</v>
       </c>
@@ -12233,7 +12217,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
         <v>535</v>
       </c>
@@ -12244,7 +12228,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A538" s="1">
         <v>536</v>
       </c>
@@ -12255,7 +12239,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
         <v>537</v>
       </c>
@@ -12266,7 +12250,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
         <v>538</v>
       </c>
@@ -12277,7 +12261,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
         <v>539</v>
       </c>
@@ -12288,7 +12272,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
         <v>540</v>
       </c>
@@ -12299,7 +12283,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
         <v>541</v>
       </c>
@@ -12310,7 +12294,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
         <v>542</v>
       </c>
@@ -12321,7 +12305,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
         <v>543</v>
       </c>
@@ -12332,7 +12316,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
         <v>544</v>
       </c>
@@ -12343,7 +12327,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
         <v>545</v>
       </c>
@@ -12354,7 +12338,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
         <v>546</v>
       </c>
@@ -12365,7 +12349,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
         <v>547</v>
       </c>
@@ -12376,7 +12360,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
         <v>548</v>
       </c>
@@ -12387,7 +12371,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
         <v>549</v>
       </c>
@@ -12398,7 +12382,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
         <v>550</v>
       </c>
@@ -12409,7 +12393,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
         <v>551</v>
       </c>
@@ -12420,7 +12404,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
         <v>552</v>
       </c>
@@ -12431,7 +12415,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
         <v>553</v>
       </c>
@@ -12442,7 +12426,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
         <v>554</v>
       </c>
@@ -12453,7 +12437,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
         <v>555</v>
       </c>
@@ -12464,7 +12448,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
         <v>556</v>
       </c>
@@ -12475,7 +12459,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
         <v>557</v>
       </c>
@@ -12486,7 +12470,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
         <v>558</v>
       </c>
@@ -12497,7 +12481,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A561" s="1">
         <v>559</v>
       </c>
@@ -12508,7 +12492,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A562" s="1">
         <v>560</v>
       </c>
@@ -12519,7 +12503,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="1">
         <v>561</v>
       </c>
@@ -12530,7 +12514,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A564" s="1">
         <v>562</v>
       </c>
@@ -12541,7 +12525,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A565" s="1">
         <v>563</v>
       </c>
@@ -12552,7 +12536,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A566" s="1">
         <v>564</v>
       </c>
@@ -12563,7 +12547,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A567" s="1">
         <v>565</v>
       </c>
@@ -12574,7 +12558,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A568" s="1">
         <v>566</v>
       </c>
@@ -12585,7 +12569,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A569" s="1">
         <v>567</v>
       </c>
@@ -12596,7 +12580,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A570" s="1">
         <v>568</v>
       </c>
@@ -12607,7 +12591,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A571" s="1">
         <v>569</v>
       </c>
@@ -12618,7 +12602,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A572" s="1">
         <v>570</v>
       </c>
@@ -12629,7 +12613,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A573" s="1">
         <v>571</v>
       </c>
@@ -12640,7 +12624,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="1">
         <v>572</v>
       </c>
@@ -12651,7 +12635,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A575" s="1">
         <v>573</v>
       </c>
@@ -12662,7 +12646,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A576" s="1">
         <v>574</v>
       </c>
@@ -12673,7 +12657,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A577" s="1">
         <v>575</v>
       </c>
@@ -12684,7 +12668,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A578" s="1">
         <v>576</v>
       </c>
@@ -12695,7 +12679,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A579" s="1">
         <v>577</v>
       </c>
@@ -12706,7 +12690,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A580" s="1">
         <v>578</v>
       </c>
@@ -12717,7 +12701,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A581" s="1">
         <v>579</v>
       </c>
@@ -12728,7 +12712,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A582" s="1">
         <v>580</v>
       </c>
@@ -12739,7 +12723,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A583" s="1">
         <v>581</v>
       </c>
@@ -12750,7 +12734,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A584" s="1">
         <v>582</v>
       </c>
@@ -12761,7 +12745,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="1">
         <v>583</v>
       </c>
@@ -12772,7 +12756,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A586" s="1">
         <v>584</v>
       </c>
@@ -12783,7 +12767,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A587" s="1">
         <v>585</v>
       </c>
@@ -12794,7 +12778,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A588" s="1">
         <v>586</v>
       </c>
@@ -12805,7 +12789,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A589" s="1">
         <v>587</v>
       </c>
@@ -12816,7 +12800,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A590" s="1">
         <v>588</v>
       </c>
@@ -12827,7 +12811,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A591" s="1">
         <v>589</v>
       </c>
@@ -12838,7 +12822,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A592" s="1">
         <v>590</v>
       </c>
@@ -12849,7 +12833,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A593" s="1">
         <v>591</v>
       </c>
@@ -12860,7 +12844,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A594" s="1">
         <v>592</v>
       </c>
@@ -12871,7 +12855,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A595" s="1">
         <v>593</v>
       </c>
@@ -12882,7 +12866,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="1">
         <v>594</v>
       </c>
@@ -12893,7 +12877,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A597" s="1">
         <v>595</v>
       </c>
@@ -12904,7 +12888,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A598" s="1">
         <v>596</v>
       </c>
@@ -12915,7 +12899,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A599" s="1">
         <v>597</v>
       </c>
@@ -12926,7 +12910,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A600" s="1">
         <v>598</v>
       </c>
@@ -12937,7 +12921,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A601" s="1">
         <v>599</v>
       </c>
@@ -12948,7 +12932,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A602" s="1">
         <v>600</v>
       </c>
@@ -12959,7 +12943,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A603" s="1">
         <v>601</v>
       </c>
@@ -12970,7 +12954,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A604" s="1">
         <v>602</v>
       </c>
@@ -12981,7 +12965,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A605" s="1">
         <v>603</v>
       </c>
@@ -12992,7 +12976,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A606" s="1">
         <v>604</v>
       </c>
@@ -13003,7 +12987,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="1">
         <v>605</v>
       </c>
@@ -13014,7 +12998,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A608" s="1">
         <v>606</v>
       </c>
@@ -13025,7 +13009,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A609" s="1">
         <v>607</v>
       </c>
@@ -13036,7 +13020,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A610" s="1">
         <v>608</v>
       </c>
@@ -13047,7 +13031,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A611" s="1">
         <v>609</v>
       </c>
@@ -13058,7 +13042,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A612" s="1">
         <v>610</v>
       </c>
@@ -13069,7 +13053,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A613" s="1">
         <v>611</v>
       </c>
@@ -13080,7 +13064,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A614" s="1">
         <v>612</v>
       </c>
@@ -13091,7 +13075,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A615" s="1">
         <v>613</v>
       </c>
@@ -13102,7 +13086,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A616" s="1">
         <v>614</v>
       </c>
@@ -13113,7 +13097,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A617" s="1">
         <v>615</v>
       </c>
@@ -13124,7 +13108,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="1">
         <v>616</v>
       </c>
@@ -13135,7 +13119,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A619" s="1">
         <v>617</v>
       </c>
@@ -13146,7 +13130,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A620" s="1">
         <v>618</v>
       </c>
@@ -13157,7 +13141,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A621" s="1">
         <v>619</v>
       </c>
@@ -13168,7 +13152,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A622" s="1">
         <v>620</v>
       </c>
@@ -13179,7 +13163,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A623" s="1">
         <v>621</v>
       </c>
@@ -13190,7 +13174,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A624" s="1">
         <v>622</v>
       </c>
@@ -13201,7 +13185,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A625" s="1">
         <v>623</v>
       </c>
@@ -13212,7 +13196,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A626" s="1">
         <v>624</v>
       </c>
@@ -13223,7 +13207,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A627" s="1">
         <v>625</v>
       </c>
@@ -13234,7 +13218,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A628" s="1">
         <v>626</v>
       </c>
@@ -13245,7 +13229,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="1">
         <v>627</v>
       </c>
@@ -13256,7 +13240,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A630" s="1">
         <v>628</v>
       </c>
@@ -13267,7 +13251,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A631" s="1">
         <v>629</v>
       </c>
@@ -13278,7 +13262,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A632" s="1">
         <v>630</v>
       </c>
@@ -13289,7 +13273,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A633" s="1">
         <v>631</v>
       </c>
@@ -13300,7 +13284,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A634" s="1">
         <v>632</v>
       </c>
@@ -13311,7 +13295,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A635" s="1">
         <v>633</v>
       </c>
@@ -13322,7 +13306,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A636" s="1">
         <v>634</v>
       </c>
@@ -13333,7 +13317,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A637" s="1">
         <v>635</v>
       </c>
@@ -13344,7 +13328,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A638" s="1">
         <v>636</v>
       </c>
@@ -13355,7 +13339,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A639" s="1">
         <v>637</v>
       </c>
@@ -13366,7 +13350,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="1">
         <v>638</v>
       </c>
@@ -13377,7 +13361,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A641" s="1">
         <v>639</v>
       </c>
@@ -13388,7 +13372,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A642" s="1">
         <v>640</v>
       </c>
@@ -13399,7 +13383,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A643" s="1">
         <v>641</v>
       </c>
@@ -13410,7 +13394,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A644" s="1">
         <v>642</v>
       </c>
@@ -13421,7 +13405,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A645" s="1">
         <v>643</v>
       </c>
@@ -13432,7 +13416,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A646" s="1">
         <v>644</v>
       </c>
@@ -13443,7 +13427,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A647" s="1">
         <v>645</v>
       </c>
@@ -13454,7 +13438,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A648" s="1">
         <v>646</v>
       </c>
@@ -13465,7 +13449,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A649" s="1">
         <v>647</v>
       </c>
@@ -13476,7 +13460,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A650" s="1">
         <v>648</v>
       </c>
@@ -13487,7 +13471,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="1">
         <v>649</v>
       </c>
@@ -13498,7 +13482,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A652" s="1">
         <v>650</v>
       </c>
@@ -13509,7 +13493,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A653" s="1">
         <v>651</v>
       </c>
@@ -13520,7 +13504,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A654" s="1">
         <v>652</v>
       </c>
@@ -13531,7 +13515,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A655" s="1">
         <v>653</v>
       </c>
@@ -13542,7 +13526,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A656" s="1">
         <v>654</v>
       </c>
@@ -13553,7 +13537,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A657" s="1">
         <v>655</v>
       </c>
@@ -13564,7 +13548,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A658" s="1">
         <v>656</v>
       </c>
@@ -13575,7 +13559,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A659" s="1">
         <v>657</v>
       </c>
@@ -13586,7 +13570,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A660" s="1">
         <v>658</v>
       </c>
@@ -13597,7 +13581,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A661" s="1">
         <v>659</v>
       </c>
@@ -13608,7 +13592,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="1">
         <v>660</v>
       </c>
@@ -13619,7 +13603,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A663" s="1">
         <v>661</v>
       </c>
@@ -13630,7 +13614,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A664" s="1">
         <v>662</v>
       </c>
@@ -13641,7 +13625,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A665" s="1">
         <v>663</v>
       </c>
@@ -13652,7 +13636,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A666" s="1">
         <v>664</v>
       </c>
@@ -13663,7 +13647,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A667" s="1">
         <v>665</v>
       </c>
@@ -13674,7 +13658,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A668" s="1">
         <v>666</v>
       </c>
@@ -13685,7 +13669,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A669" s="1">
         <v>667</v>
       </c>
@@ -13696,7 +13680,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A670" s="1">
         <v>668</v>
       </c>
@@ -13707,7 +13691,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A671" s="1">
         <v>669</v>
       </c>
@@ -13718,7 +13702,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A672" s="1">
         <v>670</v>
       </c>
@@ -13729,7 +13713,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="1">
         <v>671</v>
       </c>
@@ -13740,7 +13724,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A674" s="1">
         <v>672</v>
       </c>
@@ -13751,7 +13735,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A675" s="1">
         <v>673</v>
       </c>
@@ -13762,7 +13746,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A676" s="1">
         <v>674</v>
       </c>
@@ -13773,7 +13757,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A677" s="1">
         <v>675</v>
       </c>
@@ -13784,7 +13768,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A678" s="1">
         <v>676</v>
       </c>
@@ -13795,7 +13779,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A679" s="1">
         <v>677</v>
       </c>
@@ -13806,7 +13790,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A680" s="1">
         <v>678</v>
       </c>
@@ -13817,7 +13801,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A681" s="1">
         <v>679</v>
       </c>
@@ -13828,7 +13812,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A682" s="1">
         <v>680</v>
       </c>
@@ -13839,7 +13823,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A683" s="1">
         <v>681</v>
       </c>
@@ -13850,7 +13834,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="1">
         <v>682</v>
       </c>
@@ -13861,7 +13845,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A685" s="1">
         <v>683</v>
       </c>
@@ -13872,7 +13856,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A686" s="1">
         <v>684</v>
       </c>
@@ -13883,7 +13867,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A687" s="1">
         <v>685</v>
       </c>
@@ -13894,7 +13878,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A688" s="1">
         <v>686</v>
       </c>
@@ -13905,7 +13889,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A689" s="1">
         <v>687</v>
       </c>
@@ -13916,7 +13900,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A690" s="1">
         <v>688</v>
       </c>
@@ -13927,7 +13911,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A691" s="1">
         <v>689</v>
       </c>
@@ -13938,7 +13922,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A692" s="1">
         <v>690</v>
       </c>
@@ -13949,7 +13933,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A693" s="1">
         <v>691</v>
       </c>
@@ -13960,7 +13944,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A694" s="1">
         <v>692</v>
       </c>
@@ -13971,7 +13955,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="1">
         <v>693</v>
       </c>
@@ -13982,7 +13966,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A696" s="1">
         <v>694</v>
       </c>
@@ -13993,7 +13977,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A697" s="1">
         <v>695</v>
       </c>
@@ -14004,7 +13988,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A698" s="1">
         <v>696</v>
       </c>
@@ -14015,7 +13999,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A699" s="1">
         <v>697</v>
       </c>
@@ -14026,7 +14010,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A700" s="1">
         <v>698</v>
       </c>
@@ -14037,7 +14021,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A701" s="1">
         <v>699</v>
       </c>
@@ -14048,7 +14032,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A702" s="1">
         <v>700</v>
       </c>
@@ -14059,7 +14043,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A703" s="1">
         <v>701</v>
       </c>
@@ -14070,7 +14054,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A704" s="1">
         <v>702</v>
       </c>
@@ -14081,7 +14065,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A705" s="1">
         <v>703</v>
       </c>
@@ -14092,7 +14076,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="1">
         <v>704</v>
       </c>
@@ -14103,7 +14087,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A707" s="1">
         <v>705</v>
       </c>
@@ -14114,7 +14098,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A708" s="1">
         <v>706</v>
       </c>
@@ -14125,7 +14109,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A709" s="1">
         <v>707</v>
       </c>
@@ -14136,7 +14120,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A710" s="1">
         <v>708</v>
       </c>
@@ -14147,7 +14131,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A711" s="1">
         <v>709</v>
       </c>
@@ -14158,7 +14142,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A712" s="1">
         <v>710</v>
       </c>
@@ -14169,7 +14153,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A713" s="1">
         <v>711</v>
       </c>
@@ -14180,7 +14164,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A714" s="1">
         <v>712</v>
       </c>
@@ -14191,7 +14175,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A715" s="1">
         <v>713</v>
       </c>
@@ -14202,7 +14186,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A716" s="1">
         <v>714</v>
       </c>
@@ -14213,7 +14197,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="1">
         <v>715</v>
       </c>
@@ -14224,7 +14208,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A718" s="1">
         <v>716</v>
       </c>
@@ -14235,7 +14219,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A719" s="1">
         <v>717</v>
       </c>
@@ -14246,7 +14230,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A720" s="1">
         <v>718</v>
       </c>
@@ -14257,7 +14241,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A721" s="1">
         <v>719</v>
       </c>
@@ -14268,7 +14252,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A722" s="1">
         <v>720</v>
       </c>
@@ -14279,7 +14263,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A723" s="1">
         <v>721</v>
       </c>
@@ -14290,7 +14274,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A724" s="1">
         <v>722</v>
       </c>
@@ -14301,7 +14285,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A725" s="1">
         <v>723</v>
       </c>
@@ -14312,7 +14296,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A726" s="1">
         <v>724</v>
       </c>
@@ -14323,7 +14307,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A727" s="1">
         <v>725</v>
       </c>
@@ -14334,7 +14318,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="1">
         <v>726</v>
       </c>
@@ -14345,7 +14329,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A729" s="1">
         <v>727</v>
       </c>
@@ -14356,7 +14340,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A730" s="1">
         <v>728</v>
       </c>
@@ -14367,7 +14351,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A731" s="1">
         <v>729</v>
       </c>
@@ -14378,7 +14362,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A732" s="1">
         <v>730</v>
       </c>
@@ -14389,7 +14373,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A733" s="1">
         <v>731</v>
       </c>
@@ -14400,7 +14384,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A734" s="1">
         <v>732</v>
       </c>
@@ -14411,7 +14395,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A735" s="1">
         <v>733</v>
       </c>
@@ -14422,7 +14406,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A736" s="1">
         <v>734</v>
       </c>
@@ -14433,7 +14417,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A737" s="1">
         <v>735</v>
       </c>
@@ -14444,7 +14428,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A738" s="1">
         <v>736</v>
       </c>
@@ -14455,7 +14439,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="1">
         <v>737</v>
       </c>
@@ -14466,7 +14450,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A740" s="1">
         <v>738</v>
       </c>
@@ -14477,7 +14461,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A741" s="1">
         <v>739</v>
       </c>
@@ -14488,7 +14472,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A742" s="1">
         <v>740</v>
       </c>
@@ -14499,7 +14483,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A743" s="1">
         <v>741</v>
       </c>
@@ -14510,7 +14494,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A744" s="1">
         <v>742</v>
       </c>
@@ -14521,7 +14505,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A745" s="1">
         <v>743</v>
       </c>
@@ -14532,7 +14516,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A746" s="1">
         <v>744</v>
       </c>
@@ -14543,7 +14527,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A747" s="1">
         <v>745</v>
       </c>
@@ -14554,7 +14538,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A748" s="1">
         <v>746</v>
       </c>
@@ -14565,7 +14549,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A749" s="1">
         <v>747</v>
       </c>
@@ -14576,7 +14560,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="1">
         <v>748</v>
       </c>
@@ -14587,7 +14571,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A751" s="1">
         <v>749</v>
       </c>
@@ -14598,7 +14582,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A752" s="1">
         <v>750</v>
       </c>
@@ -14609,7 +14593,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A753" s="1">
         <v>751</v>
       </c>
@@ -14620,7 +14604,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A754" s="1">
         <v>752</v>
       </c>
@@ -14631,7 +14615,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A755" s="1">
         <v>753</v>
       </c>
@@ -14642,7 +14626,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A756" s="1">
         <v>754</v>
       </c>
@@ -14653,7 +14637,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A757" s="1">
         <v>755</v>
       </c>
@@ -14664,7 +14648,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A758" s="1">
         <v>756</v>
       </c>
@@ -14675,7 +14659,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A759" s="1">
         <v>757</v>
       </c>
@@ -14686,7 +14670,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A760" s="1">
         <v>758</v>
       </c>
@@ -14697,7 +14681,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="1">
         <v>759</v>
       </c>
@@ -14708,7 +14692,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A762" s="1">
         <v>760</v>
       </c>
@@ -14719,7 +14703,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A763" s="1">
         <v>761</v>
       </c>
@@ -14730,7 +14714,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A764" s="1">
         <v>762</v>
       </c>
@@ -14741,7 +14725,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A765" s="1">
         <v>763</v>
       </c>
@@ -14752,7 +14736,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A766" s="1">
         <v>764</v>
       </c>
@@ -14763,7 +14747,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A767" s="1">
         <v>765</v>
       </c>
@@ -14774,7 +14758,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A768" s="1">
         <v>766</v>
       </c>
@@ -14785,7 +14769,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A769" s="1">
         <v>767</v>
       </c>
@@ -14796,7 +14780,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A770" s="1">
         <v>768</v>
       </c>
@@ -14807,7 +14791,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A771" s="1">
         <v>769</v>
       </c>
@@ -14818,7 +14802,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="1">
         <v>770</v>
       </c>
@@ -14829,7 +14813,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A773" s="1">
         <v>771</v>
       </c>
@@ -14840,7 +14824,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A774" s="1">
         <v>772</v>
       </c>
@@ -14851,7 +14835,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A775" s="1">
         <v>773</v>
       </c>
@@ -14862,7 +14846,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A776" s="1">
         <v>774</v>
       </c>
@@ -14873,7 +14857,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A777" s="1">
         <v>775</v>
       </c>
@@ -14884,7 +14868,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A778" s="1">
         <v>776</v>
       </c>
@@ -14895,7 +14879,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A779" s="1">
         <v>777</v>
       </c>
@@ -14906,7 +14890,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A780" s="1">
         <v>778</v>
       </c>
@@ -14917,7 +14901,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A781" s="1">
         <v>779</v>
       </c>
@@ -14928,7 +14912,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A782" s="1">
         <v>780</v>
       </c>
@@ -14939,7 +14923,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="1">
         <v>781</v>
       </c>
@@ -14950,7 +14934,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A784" s="1">
         <v>782</v>
       </c>
@@ -14961,7 +14945,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A785" s="1">
         <v>783</v>
       </c>
@@ -14972,7 +14956,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A786" s="1">
         <v>784</v>
       </c>
@@ -14983,7 +14967,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A787" s="1">
         <v>785</v>
       </c>
@@ -14994,7 +14978,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A788" s="1">
         <v>786</v>
       </c>
@@ -15005,7 +14989,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A789" s="1">
         <v>787</v>
       </c>
@@ -15016,7 +15000,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A790" s="1">
         <v>788</v>
       </c>
@@ -15027,7 +15011,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A791" s="1">
         <v>789</v>
       </c>
@@ -15038,7 +15022,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A792" s="1">
         <v>790</v>
       </c>
@@ -15049,7 +15033,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A793" s="1">
         <v>791</v>
       </c>
@@ -15060,7 +15044,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="1">
         <v>792</v>
       </c>
@@ -15071,7 +15055,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A795" s="1">
         <v>793</v>
       </c>
@@ -15082,7 +15066,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A796" s="1">
         <v>794</v>
       </c>
@@ -15093,7 +15077,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A797" s="1">
         <v>795</v>
       </c>
@@ -15104,7 +15088,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A798" s="1">
         <v>796</v>
       </c>
@@ -15115,7 +15099,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A799" s="1">
         <v>797</v>
       </c>
@@ -15126,7 +15110,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A800" s="1">
         <v>798</v>
       </c>
@@ -15153,12 +15137,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E979BB-8C26-46D3-9A93-08BA0230DF6E}">
   <dimension ref="B2:C78"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1639</v>
       </c>
@@ -15166,7 +15150,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>392</v>
       </c>
@@ -15174,7 +15158,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>394</v>
       </c>
@@ -15182,7 +15166,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>396</v>
       </c>
@@ -15190,7 +15174,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>398</v>
       </c>
@@ -15198,7 +15182,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>400</v>
       </c>
@@ -15206,7 +15190,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>402</v>
       </c>
@@ -15214,7 +15198,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>404</v>
       </c>
@@ -15222,7 +15206,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>406</v>
       </c>
@@ -15230,7 +15214,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>408</v>
       </c>
@@ -15238,7 +15222,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>410</v>
       </c>
@@ -15246,7 +15230,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>412</v>
       </c>
@@ -15254,7 +15238,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>414</v>
       </c>
@@ -15262,7 +15246,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>416</v>
       </c>
@@ -15270,7 +15254,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>432</v>
       </c>
@@ -15278,7 +15262,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>434</v>
       </c>
@@ -15286,7 +15270,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>438</v>
       </c>
@@ -15294,7 +15278,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>440</v>
       </c>
@@ -15302,7 +15286,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>442</v>
       </c>
@@ -15310,7 +15294,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>444</v>
       </c>
@@ -15318,7 +15302,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>446</v>
       </c>
@@ -15326,7 +15310,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>448</v>
       </c>
@@ -15334,7 +15318,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>450</v>
       </c>
@@ -15342,7 +15326,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>452</v>
       </c>
@@ -15350,7 +15334,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>872</v>
       </c>
@@ -15358,7 +15342,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>874</v>
       </c>
@@ -15366,7 +15350,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>890</v>
       </c>
@@ -15374,7 +15358,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>894</v>
       </c>
@@ -15382,7 +15366,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>896</v>
       </c>
@@ -15390,7 +15374,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>898</v>
       </c>
@@ -15398,7 +15382,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>900</v>
       </c>
@@ -15406,7 +15390,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>902</v>
       </c>
@@ -15414,7 +15398,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>904</v>
       </c>
@@ -15422,7 +15406,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>908</v>
       </c>
@@ -15430,7 +15414,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>912</v>
       </c>
@@ -15438,7 +15422,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>916</v>
       </c>
@@ -15446,7 +15430,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>918</v>
       </c>
@@ -15454,7 +15438,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>920</v>
       </c>
@@ -15462,7 +15446,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>926</v>
       </c>
@@ -15470,7 +15454,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>930</v>
       </c>
@@ -15478,7 +15462,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>934</v>
       </c>
@@ -15486,7 +15470,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>938</v>
       </c>
@@ -15494,7 +15478,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>940</v>
       </c>
@@ -15502,7 +15486,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
         <v>942</v>
       </c>
@@ -15510,7 +15494,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
         <v>944</v>
       </c>
@@ -15518,7 +15502,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>946</v>
       </c>
@@ -15526,7 +15510,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
         <v>950</v>
       </c>
@@ -15534,7 +15518,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>1306</v>
       </c>
@@ -15542,7 +15526,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
         <v>1310</v>
       </c>
@@ -15550,7 +15534,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>1312</v>
       </c>
@@ -15558,7 +15542,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
         <v>1316</v>
       </c>
@@ -15566,7 +15550,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
         <v>1318</v>
       </c>
@@ -15574,7 +15558,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
         <v>1320</v>
       </c>
@@ -15582,7 +15566,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
         <v>1322</v>
       </c>
@@ -15590,7 +15574,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>1326</v>
       </c>
@@ -15598,7 +15582,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>1328</v>
       </c>
@@ -15606,7 +15590,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
         <v>1330</v>
       </c>
@@ -15614,7 +15598,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
         <v>1332</v>
       </c>
@@ -15622,7 +15606,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
         <v>1334</v>
       </c>
@@ -15630,7 +15614,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>1336</v>
       </c>
@@ -15638,7 +15622,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
         <v>1338</v>
       </c>
@@ -15646,7 +15630,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
         <v>1340</v>
       </c>
@@ -15654,7 +15638,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
         <v>1342</v>
       </c>
@@ -15662,7 +15646,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
         <v>1344</v>
       </c>
@@ -15670,7 +15654,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>1346</v>
       </c>
@@ -15678,7 +15662,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
         <v>1350</v>
       </c>
@@ -15686,7 +15670,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
         <v>1356</v>
       </c>
@@ -15694,7 +15678,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
         <v>1358</v>
       </c>
@@ -15702,7 +15686,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
         <v>1360</v>
       </c>
@@ -15710,7 +15694,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
         <v>1366</v>
       </c>
@@ -15718,7 +15702,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
         <v>1368</v>
       </c>
@@ -15726,7 +15710,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
         <v>1370</v>
       </c>
@@ -15734,7 +15718,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
         <v>1372</v>
       </c>
@@ -15742,7 +15726,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
         <v>1376</v>
       </c>
@@ -15750,7 +15734,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
         <v>1378</v>
       </c>
@@ -15758,7 +15742,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
         <v>1380</v>
       </c>
@@ -15766,7 +15750,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
         <v>1382</v>
       </c>
@@ -15785,15 +15769,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920D420D-BAB7-4AC9-99B8-8EA6C39CC898}">
   <dimension ref="B2:C29"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="2"/>
-    <col min="2" max="2" width="19.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="88.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="19.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>1600</v>
       </c>
@@ -15801,7 +15785,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>1601</v>
       </c>
@@ -15809,7 +15793,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>1604</v>
       </c>
@@ -15817,7 +15801,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" ht="32" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>1074</v>
       </c>
@@ -15825,7 +15809,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>622</v>
       </c>
@@ -15833,7 +15817,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>618</v>
       </c>
@@ -15841,17 +15825,17 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>1608</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>1609</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>1611</v>
       </c>
@@ -15859,7 +15843,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
@@ -15867,7 +15851,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>660</v>
       </c>
@@ -15875,7 +15859,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>1615</v>
       </c>
@@ -15883,17 +15867,17 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>1617</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>600</v>
       </c>
@@ -15901,7 +15885,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>1619</v>
       </c>
@@ -15909,7 +15893,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>1621</v>
       </c>
@@ -15917,7 +15901,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>1623</v>
       </c>
@@ -15925,7 +15909,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>606</v>
       </c>
@@ -15933,7 +15917,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>1626</v>
       </c>
@@ -15941,22 +15925,22 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>1628</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>1629</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>1630</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>1631</v>
       </c>
@@ -15964,7 +15948,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>1634</v>
       </c>
@@ -15972,12 +15956,12 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>1635</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>1636</v>
       </c>
@@ -15985,7 +15969,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>1638</v>
       </c>
@@ -16004,20 +15988,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAEC944D-C38C-4479-A2AA-B5B777D146F4}">
   <dimension ref="A1:I80"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" style="2" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="39.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="2"/>
+    <col min="4" max="4" width="80.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="39.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>1656</v>
       </c>
@@ -16043,7 +16027,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1727</v>
       </c>
@@ -16060,13 +16044,13 @@
         <v>1811</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>1835</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1658</v>
       </c>
@@ -16081,14 +16065,14 @@
         <v>1811</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>1840</v>
       </c>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1677</v>
       </c>
@@ -16103,14 +16087,14 @@
         <v>1811</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>1850</v>
       </c>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1823</v>
       </c>
@@ -16122,14 +16106,14 @@
         <v>1811</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>1862</v>
       </c>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1702</v>
       </c>
@@ -16146,14 +16130,14 @@
         <v>1811</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>1826</v>
       </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1702</v>
       </c>
@@ -16168,7 +16152,7 @@
       <c r="G7" s="5"/>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1721</v>
       </c>
@@ -16185,14 +16169,14 @@
         <v>1811</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>1827</v>
       </c>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1680</v>
       </c>
@@ -16209,14 +16193,14 @@
         <v>1811</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>1828</v>
       </c>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1756</v>
       </c>
@@ -16224,7 +16208,7 @@
         <v>1751</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>1782</v>
@@ -16233,13 +16217,13 @@
         <v>1811</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>1905</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1650</v>
       </c>
@@ -16254,13 +16238,13 @@
         <v>1811</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>1829</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1667</v>
       </c>
@@ -16272,7 +16256,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>1667</v>
       </c>
@@ -16287,13 +16271,13 @@
         <v>1811</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>1830</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1666</v>
       </c>
@@ -16308,13 +16292,13 @@
         <v>1811</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>1831</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1688</v>
       </c>
@@ -16323,7 +16307,7 @@
       </c>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1688</v>
       </c>
@@ -16338,13 +16322,13 @@
         <v>1811</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>1832</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1688</v>
       </c>
@@ -16353,7 +16337,7 @@
       </c>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1609</v>
       </c>
@@ -16370,13 +16354,13 @@
         <v>1811</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>1833</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1726</v>
       </c>
@@ -16391,13 +16375,13 @@
         <v>1811</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>1834</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1726</v>
       </c>
@@ -16411,7 +16395,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>1726</v>
       </c>
@@ -16423,7 +16407,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>1622</v>
       </c>
@@ -16440,13 +16424,13 @@
         <v>1811</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>1836</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>1622</v>
       </c>
@@ -16460,7 +16444,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>1622</v>
       </c>
@@ -16472,7 +16456,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>1744</v>
       </c>
@@ -16492,7 +16476,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>1684</v>
       </c>
@@ -16512,7 +16496,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>1684</v>
       </c>
@@ -16532,7 +16516,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>1736</v>
       </c>
@@ -16549,13 +16533,13 @@
         <v>1811</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>1837</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>1682</v>
       </c>
@@ -16572,13 +16556,13 @@
         <v>1811</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>1838</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>1746</v>
       </c>
@@ -16595,13 +16579,13 @@
         <v>1811</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>1839</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1696</v>
       </c>
@@ -16616,13 +16600,13 @@
         <v>1811</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>1841</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>1696</v>
       </c>
@@ -16634,7 +16618,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>1691</v>
       </c>
@@ -16649,13 +16633,13 @@
         <v>1811</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1691</v>
       </c>
@@ -16667,7 +16651,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1676</v>
       </c>
@@ -16682,13 +16666,13 @@
         <v>1811</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>1843</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>1676</v>
       </c>
@@ -16697,7 +16681,7 @@
       </c>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>1676</v>
       </c>
@@ -16706,7 +16690,7 @@
       </c>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>1748</v>
       </c>
@@ -16721,13 +16705,13 @@
         <v>1811</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>1844</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>1664</v>
       </c>
@@ -16744,13 +16728,13 @@
         <v>1811</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>1845</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>1693</v>
       </c>
@@ -16765,13 +16749,13 @@
         <v>1811</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>1846</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>1649</v>
       </c>
@@ -16786,13 +16770,13 @@
         <v>1811</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>1847</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>1649</v>
       </c>
@@ -16804,7 +16788,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>1662</v>
       </c>
@@ -16821,13 +16805,13 @@
         <v>1811</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>1848</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>1721</v>
       </c>
@@ -16844,13 +16828,13 @@
         <v>1811</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>1849</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>1704</v>
       </c>
@@ -16869,7 +16853,7 @@
       </c>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>1704</v>
       </c>
@@ -16878,7 +16862,7 @@
       </c>
       <c r="C46" s="3"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>1707</v>
       </c>
@@ -16893,13 +16877,13 @@
         <v>1811</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>1851</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>1660</v>
       </c>
@@ -16914,13 +16898,13 @@
         <v>1811</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>1852</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>1698</v>
       </c>
@@ -16935,13 +16919,13 @@
         <v>1811</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>1853</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>1672</v>
       </c>
@@ -16956,13 +16940,13 @@
         <v>1811</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>1854</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>1672</v>
       </c>
@@ -16974,7 +16958,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>1700</v>
       </c>
@@ -16989,13 +16973,13 @@
         <v>1811</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>1855</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>1652</v>
       </c>
@@ -17013,7 +16997,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>1652</v>
       </c>
@@ -17025,7 +17009,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>1652</v>
       </c>
@@ -17037,7 +17021,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>1742</v>
       </c>
@@ -17055,7 +17039,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>1734</v>
       </c>
@@ -17067,7 +17051,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>1734</v>
       </c>
@@ -17079,7 +17063,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>1734</v>
       </c>
@@ -17091,7 +17075,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>1734</v>
       </c>
@@ -17103,7 +17087,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>452</v>
       </c>
@@ -17121,7 +17105,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>452</v>
       </c>
@@ -17139,7 +17123,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>452</v>
       </c>
@@ -17151,7 +17135,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>452</v>
       </c>
@@ -17163,7 +17147,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>1709</v>
       </c>
@@ -17180,13 +17164,13 @@
         <v>1811</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>1856</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>1709</v>
       </c>
@@ -17200,7 +17184,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>1709</v>
       </c>
@@ -17214,7 +17198,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>1709</v>
       </c>
@@ -17228,7 +17212,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>1719</v>
       </c>
@@ -17245,13 +17229,13 @@
         <v>1811</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>1857</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>1717</v>
       </c>
@@ -17266,13 +17250,13 @@
         <v>1811</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>1858</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>1717</v>
       </c>
@@ -17284,7 +17268,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>1717</v>
       </c>
@@ -17298,7 +17282,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>1732</v>
       </c>
@@ -17313,13 +17297,13 @@
         <v>1811</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>1859</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>1732</v>
       </c>
@@ -17333,7 +17317,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>448</v>
       </c>
@@ -17348,13 +17332,13 @@
         <v>1811</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>1860</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
         <v>1815</v>
       </c>
@@ -17363,7 +17347,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>1816</v>
       </c>
@@ -17380,13 +17364,13 @@
         <v>1811</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>1861</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>1819</v>
       </c>
@@ -17397,7 +17381,7 @@
         <v>1821</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>1820</v>
@@ -17406,7 +17390,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>1819</v>
       </c>
@@ -17417,34 +17401,34 @@
         <v>1863</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>1864</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>1811</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="2" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>1811</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicoerosanna/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761AF600-AE6C-7A41-8637-6676E943E24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B077C-6F2E-4A46-B1AB-6AB4433C4D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Originale" sheetId="1" r:id="rId1"/>
     <sheet name="Countries" sheetId="3" r:id="rId2"/>
     <sheet name="Aree Interessanti" sheetId="2" r:id="rId3"/>
     <sheet name="ETFs" sheetId="4" r:id="rId4"/>
+    <sheet name="Bond" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Originale!$A$1:$C$800</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="1911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="1931">
   <si>
     <t>name</t>
   </si>
@@ -5772,6 +5773,66 @@
   </si>
   <si>
     <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/gold/Gold_price_averages_in_a%20range_of_currencies_since_1978.xlsx</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
+    <t>FR0013451507</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Obligaciones Tf 0,6% Ot29 Eur</t>
+  </si>
+  <si>
+    <t>Btp Tf 1,65% Dc30 Eur</t>
+  </si>
+  <si>
+    <t>Btp Tf 2,65% Dc27 Eur</t>
+  </si>
+  <si>
+    <t>Oat Tf 0% Nv30 Eur</t>
+  </si>
+  <si>
+    <t>Oat Tf 0,75% Nv28 Eur</t>
+  </si>
+  <si>
+    <t>Oat Tf 0% Nv29 Eur</t>
+  </si>
+  <si>
+    <t>ES0000012F43</t>
+  </si>
+  <si>
+    <t>IT0005413171</t>
+  </si>
+  <si>
+    <t>IT0005500068</t>
+  </si>
+  <si>
+    <t>FR0013516549</t>
+  </si>
+  <si>
+    <t>FR0013341682</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/ES0000012F43%20Overview.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013341682%20Overview.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013451507%20Overview.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013516549%20Overview.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/IT0005413171%20Overview.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/IT0005500068%20Overview.csv</t>
   </si>
 </sst>
 </file>
@@ -16089,7 +16150,7 @@
       <c r="G4" s="9" t="s">
         <v>1894</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>1850</v>
       </c>
       <c r="I4" s="5"/>
@@ -17231,7 +17292,7 @@
       <c r="G69" s="7" t="s">
         <v>1889</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" s="7" t="s">
         <v>1857</v>
       </c>
     </row>
@@ -17455,12 +17516,110 @@
     <hyperlink ref="G10" r:id="rId19" xr:uid="{BF16DD84-9AE8-4A58-939F-C68B34E56906}"/>
     <hyperlink ref="H80" r:id="rId20" xr:uid="{C12C3366-52FB-6A42-98A1-F4D2EB64B47C}"/>
     <hyperlink ref="G80" r:id="rId21" xr:uid="{F84C9AE7-E47A-4F40-A757-19B9FB43DC6A}"/>
+    <hyperlink ref="G69" r:id="rId22" xr:uid="{B043322A-450B-D945-86BE-F9D3053DC051}"/>
+    <hyperlink ref="H69" r:id="rId23" xr:uid="{08777C01-AD46-7C4B-B0A2-B07D4AC73913}"/>
+    <hyperlink ref="H4" r:id="rId24" xr:uid="{ABE20F3E-5342-3A4B-BAD0-7D57D91659BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId22"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId25"/>
   <tableParts count="1">
-    <tablePart r:id="rId23"/>
+    <tablePart r:id="rId26"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9FC00F-03C5-1D43-9B10-708272D13D63}">
+  <dimension ref="B2:D8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{A849DEE4-60D9-AC49-A823-05CD52A5C152}"/>
+    <hyperlink ref="D7" r:id="rId2" xr:uid="{AA81CF57-8557-334D-A88D-C065EB294720}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicoerosanna/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B077C-6F2E-4A46-B1AB-6AB4433C4D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAD8629-089B-3E4E-8650-E8CB3F3BC5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Originale" sheetId="1" r:id="rId1"/>
@@ -5769,9 +5769,6 @@
     <t>https://www.msci.com/indexes/index/664204</t>
   </si>
   <si>
-    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/664204%20-%20MSCI%20ACWI%20IMI%20Index.xlsx</t>
-  </si>
-  <si>
     <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/gold/Gold_price_averages_in_a%20range_of_currencies_since_1978.xlsx</t>
   </si>
   <si>
@@ -5833,6 +5830,9 @@
   </si>
   <si>
     <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/IT0005500068%20Overview.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/664204%20-%20MSCI%20ACWI%20IMI%20Index%20.xlsx</t>
   </si>
 </sst>
 </file>
@@ -5947,6 +5947,44 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5981,44 +6019,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6039,7 +6039,7 @@
     <sortCondition ref="A1:A800"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D73B884A-503A-4A59-8C87-18B439C847EE}" name="id" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{D73B884A-503A-4A59-8C87-18B439C847EE}" name="id" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{5A90A855-91ED-41CE-B4B6-41473BC05892}" name="name"/>
     <tableColumn id="3" xr3:uid="{A6DB99C2-C65F-4DE9-8199-32DE52DA7D1D}" name="url"/>
   </tableColumns>
@@ -6059,31 +6059,31 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}" name="Table1" displayName="Table1" ref="B2:C30" totalsRowShown="0" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}" name="Table1" displayName="Table1" ref="B2:C30" totalsRowShown="0" dataDxfId="13">
   <autoFilter ref="B2:C30" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2DEF44DB-B91A-4361-87EC-E5D8D821409D}" name="Aree" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{8FBA11E1-52C6-43A5-A4B9-0B712AC388F0}" name="Note" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{2DEF44DB-B91A-4361-87EC-E5D8D821409D}" name="Aree" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{8FBA11E1-52C6-43A5-A4B9-0B712AC388F0}" name="Note" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}" name="Table2" displayName="Table2" ref="A1:H80" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}" name="Table2" displayName="Table2" ref="A1:H80" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:H80" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H79">
-    <sortCondition sortBy="cellColor" ref="G1:G79" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="G1:G79" dxfId="8"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{60FD31BC-5634-4AC8-90B2-A3D616FBC3D6}" name="Country/Area" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{540470DD-A2B3-4E39-8556-EA289CFDD467}" name="ETF" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{D752676A-DDD5-4EF0-B155-46198ABE56FB}" name="Note" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{67AF040E-FE41-4ECF-B4E6-99DBE8F70E46}" name="Data label" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{B3443B95-6046-496C-8F37-29C6A0B5F077}" name="Data source" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{3D3BC678-D548-42C9-BDDE-6FBC4D8160B8}" name="Yahoo" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{66183E1C-249B-4B92-B75F-97E586BFDF95}" name="Link" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{89FD6C47-21B3-47AF-97FD-B2BF9E03DF02}" name="Original source" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{60FD31BC-5634-4AC8-90B2-A3D616FBC3D6}" name="Country/Area" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{540470DD-A2B3-4E39-8556-EA289CFDD467}" name="ETF" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{D752676A-DDD5-4EF0-B155-46198ABE56FB}" name="Note" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{67AF040E-FE41-4ECF-B4E6-99DBE8F70E46}" name="Data label" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{B3443B95-6046-496C-8F37-29C6A0B5F077}" name="Data source" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{3D3BC678-D548-42C9-BDDE-6FBC4D8160B8}" name="Yahoo" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{66183E1C-249B-4B92-B75F-97E586BFDF95}" name="Link" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{89FD6C47-21B3-47AF-97FD-B2BF9E03DF02}" name="Original source" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17468,7 +17468,7 @@
         <v>1864</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -17486,7 +17486,7 @@
         <v>1811</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>1909</v>
+        <v>1930</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>1908</v>
@@ -17539,10 +17539,10 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="C2" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="D2" t="s">
         <v>1779</v>
@@ -17550,68 +17550,68 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="C3" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="C4" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="D4" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="C5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D5" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C6" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="D6" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C7" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C8" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="D8" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicoerosanna/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAD8629-089B-3E4E-8650-E8CB3F3BC5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BDA530-C35C-B648-B8AD-A5C5B3B1E165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Originale" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="1931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2230" uniqueCount="1934">
   <si>
     <t>name</t>
   </si>
@@ -5814,25 +5814,34 @@
     <t>FR0013341682</t>
   </si>
   <si>
-    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/ES0000012F43%20Overview.csv</t>
-  </si>
-  <si>
-    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013341682%20Overview.csv</t>
-  </si>
-  <si>
-    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013451507%20Overview.csv</t>
-  </si>
-  <si>
-    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013516549%20Overview.csv</t>
-  </si>
-  <si>
-    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/IT0005413171%20Overview.csv</t>
-  </si>
-  <si>
-    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/IT0005500068%20Overview.csv</t>
-  </si>
-  <si>
     <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/664204%20-%20MSCI%20ACWI%20IMI%20Index%20.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/ES0000012F43.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/IT0005413171.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/IT0005500068.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013516549.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013341682.csv</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/FR0013451507.csv</t>
+  </si>
+  <si>
+    <t>BE0000351602</t>
+  </si>
+  <si>
+    <t>https://github.com/nicogiangregorio/Stock-Indexes-Historical-Data/raw/refs/heads/main/data/bond/BE0000351602.csv</t>
+  </si>
+  <si>
+    <t>Belgium Tf 0% Ot27 Eur</t>
   </si>
 </sst>
 </file>
@@ -5947,44 +5956,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6019,6 +5990,44 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6039,7 +6048,7 @@
     <sortCondition ref="A1:A800"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D73B884A-503A-4A59-8C87-18B439C847EE}" name="id" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{D73B884A-503A-4A59-8C87-18B439C847EE}" name="id" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{5A90A855-91ED-41CE-B4B6-41473BC05892}" name="name"/>
     <tableColumn id="3" xr3:uid="{A6DB99C2-C65F-4DE9-8199-32DE52DA7D1D}" name="url"/>
   </tableColumns>
@@ -6059,31 +6068,31 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}" name="Table1" displayName="Table1" ref="B2:C30" totalsRowShown="0" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}" name="Table1" displayName="Table1" ref="B2:C30" totalsRowShown="0" dataDxfId="2">
   <autoFilter ref="B2:C30" xr:uid="{B825CB39-3FB6-4064-ADC4-67E15DF50881}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2DEF44DB-B91A-4361-87EC-E5D8D821409D}" name="Aree" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{8FBA11E1-52C6-43A5-A4B9-0B712AC388F0}" name="Note" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{2DEF44DB-B91A-4361-87EC-E5D8D821409D}" name="Aree" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{8FBA11E1-52C6-43A5-A4B9-0B712AC388F0}" name="Note" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}" name="Table2" displayName="Table2" ref="A1:H80" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}" name="Table2" displayName="Table2" ref="A1:H80" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:H80" xr:uid="{82EB5BE7-D412-4225-A998-057E67F8DA2F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H79">
-    <sortCondition sortBy="cellColor" ref="G1:G79" dxfId="8"/>
+    <sortCondition sortBy="cellColor" ref="G1:G79" dxfId="12"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{60FD31BC-5634-4AC8-90B2-A3D616FBC3D6}" name="Country/Area" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{540470DD-A2B3-4E39-8556-EA289CFDD467}" name="ETF" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{D752676A-DDD5-4EF0-B155-46198ABE56FB}" name="Note" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{67AF040E-FE41-4ECF-B4E6-99DBE8F70E46}" name="Data label" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{B3443B95-6046-496C-8F37-29C6A0B5F077}" name="Data source" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{3D3BC678-D548-42C9-BDDE-6FBC4D8160B8}" name="Yahoo" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{66183E1C-249B-4B92-B75F-97E586BFDF95}" name="Link" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{89FD6C47-21B3-47AF-97FD-B2BF9E03DF02}" name="Original source" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{60FD31BC-5634-4AC8-90B2-A3D616FBC3D6}" name="Country/Area" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{540470DD-A2B3-4E39-8556-EA289CFDD467}" name="ETF" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{D752676A-DDD5-4EF0-B155-46198ABE56FB}" name="Note" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{67AF040E-FE41-4ECF-B4E6-99DBE8F70E46}" name="Data label" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{B3443B95-6046-496C-8F37-29C6A0B5F077}" name="Data source" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{3D3BC678-D548-42C9-BDDE-6FBC4D8160B8}" name="Yahoo" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{66183E1C-249B-4B92-B75F-97E586BFDF95}" name="Link" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{89FD6C47-21B3-47AF-97FD-B2BF9E03DF02}" name="Original source" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17486,7 +17495,7 @@
         <v>1811</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>1908</v>
@@ -17530,7 +17539,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9FC00F-03C5-1D43-9B10-708272D13D63}">
-  <dimension ref="B2:D8"/>
+  <dimension ref="B2:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -17556,7 +17565,7 @@
         <v>1913</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
@@ -17567,7 +17576,7 @@
         <v>1914</v>
       </c>
       <c r="D4" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
@@ -17578,7 +17587,7 @@
         <v>1915</v>
       </c>
       <c r="D5" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
@@ -17589,7 +17598,7 @@
         <v>1916</v>
       </c>
       <c r="D6" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
@@ -17600,7 +17609,7 @@
         <v>1917</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1925</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
@@ -17611,14 +17620,21 @@
         <v>1918</v>
       </c>
       <c r="D8" t="s">
-        <v>1926</v>
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1932</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{A849DEE4-60D9-AC49-A823-05CD52A5C152}"/>
-    <hyperlink ref="D7" r:id="rId2" xr:uid="{AA81CF57-8557-334D-A88D-C065EB294720}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
